--- a/public/templates/termo_parceria.xlsx
+++ b/public/templates/termo_parceria.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orientacoes" sheetId="1" r:id="R3b56c1c4d9934681"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ajuste" sheetId="2" r:id="R24435674067f45c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contratos" sheetId="3" r:id="R057c0bb0406c4177"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Naturezas_Contrato" sheetId="4" r:id="R485f5de78f024c60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documentos_Fiscais" sheetId="5" r:id="Ra618d371ff0841db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pagamentos" sheetId="6" r:id="R3c027febbd0b4b7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funcionarios" sheetId="7" r:id="Rf91fc10ef07d4594"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Salarios" sheetId="8" r:id="R3222e3cc595c4d9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remuneracoes_Func" sheetId="9" r:id="R7fc62b47cfc24536"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servidores_Cedidos" sheetId="10" r:id="Rf20950c61ba049c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remuneracoes_Cedidos" sheetId="11" r:id="Rd895838b945242af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dicionario" sheetId="12" r:id="Re2cba628227547f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orientacoes" sheetId="1" r:id="R7ef663ed1efb4d66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ajuste" sheetId="2" r:id="Rcedd1e70ffe345a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contratos" sheetId="3" r:id="Ra8af0ec5bdf0435a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Naturezas_Contrato" sheetId="4" r:id="R05f13177a8be4d0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documentos_Fiscais" sheetId="5" r:id="Rc703019575444b26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pagamentos" sheetId="6" r:id="R3eb796966e7e4211"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funcionarios" sheetId="7" r:id="Ra6a4e5ca171f401e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Salarios" sheetId="8" r:id="R8d6a805013734e33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remuneracoes_Func" sheetId="9" r:id="Rb1425626203f4e33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servidores_Cedidos" sheetId="10" r:id="Reee8dbfa58224d24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remuneracoes_Cedidos" sheetId="11" r:id="Ref42410af01d4b40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dicionario" sheetId="12" r:id="R6ba4162e996644e5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -401,10 +401,10 @@
     </x:row>
     <x:row r="11" ht="26" customHeight="1">
       <x:c r="A11" s="1" t="str">
-        <x:v>CSV alternativo</x:v>
+        <x:v>Arquivo de carga</x:v>
       </x:c>
       <x:c r="B11" s="1" t="str">
-        <x:v>Um CSV UTF-8 por aba. Use o nome da aba como nome do arquivo. Ajuste.csv é obrigatório.</x:v>
+        <x:v>Envie somente um arquivo XLSX com todas as abas do ajuste.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="26" customHeight="1">
